--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>122250585</v>
       </c>
       <c r="B11" t="n">
-        <v>43061</v>
+        <v>43066</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1801,11 +1801,6 @@
       <c r="E11" t="n">
         <v>101509</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Apollofjäril</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Parnassius apollo</t>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>122250585</v>
       </c>
       <c r="B11" t="n">
-        <v>43066</v>
+        <v>43070</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,6 +1800,11 @@
       </c>
       <c r="E11" t="n">
         <v>101509</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Apollofjäril</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>122250585</v>
       </c>
       <c r="B11" t="n">
-        <v>43070</v>
+        <v>43071</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,259 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123749854</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alskog, Smaulmyrar SV om, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>717440</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6362574</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alskog</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>I-Got-3362</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-06-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-07-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Oxenstierna</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123749813</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Smaulmyrar V-del 300 m SV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>717266</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6362795</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alskog</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>I-Got-3386</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2000-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2000-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 fertilt ex.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>123749854</v>
       </c>
       <c r="B12" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>123749813</v>
       </c>
       <c r="B13" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 66053-2019 artfynd.xlsx
+++ b/artfynd/A 66053-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,259 +1910,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>123749854</v>
-      </c>
-      <c r="B12" t="n">
-        <v>102630</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6037533</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garderönn</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Sorbus atrata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Alskog, Smaulmyrar SV om, Gtl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>717440</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6362574</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Alskog</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>I-Got-3362</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2018-07-09</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Andreas Oxenstierna</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>123749813</v>
-      </c>
-      <c r="B13" t="n">
-        <v>102630</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6037533</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garderönn</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Sorbus atrata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Smaulmyrar V-del 300 m SV, Gtl</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>717266</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6362795</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Alskog</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>I-Got-3386</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2000-08-07</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2000-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 fertilt ex.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkberg.</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
